--- a/resultados_algoritmos/prueba_F_varianzas.xlsx
+++ b/resultados_algoritmos/prueba_F_varianzas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,11 +464,6 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>valor_p</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t>decision</t>
         </is>
       </c>
@@ -483,13 +478,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0002317264943304051</v>
+        <v>0.0003704779512720289</v>
       </c>
       <c r="D2" t="n">
-        <v>7.866336128705166e-05</v>
+        <v>0.0002475084539854355</v>
       </c>
       <c r="E2" t="n">
-        <v>2.94579955062953</v>
+        <v>1.496829483221731</v>
       </c>
       <c r="F2" t="n">
         <v>99</v>
@@ -498,15 +493,12 @@
         <v>99</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I2" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J2" t="n">
-        <v>1.613338949760214e-07</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -522,13 +514,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002317264943304051</v>
+        <v>0.0003704779512720289</v>
       </c>
       <c r="D3" t="n">
-        <v>3.944939591273488e-05</v>
+        <v>7.587553910319367e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>5.874018827639391</v>
+        <v>4.882706016337683</v>
       </c>
       <c r="F3" t="n">
         <v>99</v>
@@ -537,15 +529,12 @@
         <v>99</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I3" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J3" t="n">
-        <v>1.06807384109576e-16</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -561,13 +550,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.866336128705166e-05</v>
+        <v>0.0002475084539854355</v>
       </c>
       <c r="D4" t="n">
-        <v>3.944939591273488e-05</v>
+        <v>7.587553910319367e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.994032087615768</v>
+        <v>3.262032229501716</v>
       </c>
       <c r="F4" t="n">
         <v>99</v>
@@ -576,15 +565,12 @@
         <v>99</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I4" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.0006943084466872958</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -600,13 +586,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.00268902643521802</v>
+        <v>0.005290490342966861</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006677167359987976</v>
+        <v>0.004563859959036312</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4027196399676377</v>
+        <v>1.159213996584589</v>
       </c>
       <c r="F5" t="n">
         <v>99</v>
@@ -615,17 +601,14 @@
         <v>99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I5" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J5" t="n">
-        <v>9.029515440383263e-06</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Se rechaza H0</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No se rechaza H0</t>
         </is>
       </c>
     </row>
@@ -639,13 +622,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00268902643521802</v>
+        <v>0.005290490342966861</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009847561078698808</v>
+        <v>8.184304173084935e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.730652202843031</v>
+        <v>64.64190762075134</v>
       </c>
       <c r="F6" t="n">
         <v>99</v>
@@ -654,15 +637,12 @@
         <v>99</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I6" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.029378274934275e-06</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -678,13 +658,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006677167359987976</v>
+        <v>0.004563859959036312</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009847561078698808</v>
+        <v>8.184304173084935e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.780529012844928</v>
+        <v>55.76356721986351</v>
       </c>
       <c r="F7" t="n">
         <v>99</v>
@@ -693,15 +673,12 @@
         <v>99</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I7" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J7" t="n">
-        <v>5.864842040409758e-19</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -717,13 +694,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01450587637775812</v>
+        <v>0.04459549578144188</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007555738580247523</v>
+        <v>0.02285683263802575</v>
       </c>
       <c r="E8" t="n">
-        <v>1.919848896794801</v>
+        <v>1.951079420656501</v>
       </c>
       <c r="F8" t="n">
         <v>99</v>
@@ -732,15 +709,12 @@
         <v>99</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I8" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.001333122080892271</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -756,13 +730,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01450587637775812</v>
+        <v>0.04459549578144188</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002882249787542612</v>
+        <v>0.0004040028083405396</v>
       </c>
       <c r="E9" t="n">
-        <v>50.32831103138267</v>
+        <v>110.3841232307764</v>
       </c>
       <c r="F9" t="n">
         <v>99</v>
@@ -771,15 +745,12 @@
         <v>99</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I9" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J9" t="n">
-        <v>4.327850473466078e-57</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -795,13 +766,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.007555738580247523</v>
+        <v>0.02285683263802575</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002882249787542612</v>
+        <v>0.0004040028083405396</v>
       </c>
       <c r="E10" t="n">
-        <v>26.21472508352407</v>
+        <v>56.57592513257831</v>
       </c>
       <c r="F10" t="n">
         <v>99</v>
@@ -810,15 +781,12 @@
         <v>99</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I10" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J10" t="n">
-        <v>8.125315031320877e-44</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -834,13 +802,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2980608790674545</v>
+        <v>0.3484503573819249</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3075329594160498</v>
+        <v>0.1285442467678688</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9691997879948182</v>
+        <v>2.710742535301271</v>
       </c>
       <c r="F11" t="n">
         <v>99</v>
@@ -849,17 +817,14 @@
         <v>99</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I11" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.8766299196758532</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>No se rechaza H0</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Se rechaza H0</t>
         </is>
       </c>
     </row>
@@ -873,13 +838,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2980608790674545</v>
+        <v>0.3484503573819249</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008052894898691507</v>
+        <v>0.009040690178982387</v>
       </c>
       <c r="E12" t="n">
-        <v>370.128857779934</v>
+        <v>38.5424509062367</v>
       </c>
       <c r="F12" t="n">
         <v>99</v>
@@ -888,15 +853,12 @@
         <v>99</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I12" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J12" t="n">
-        <v>2.869580867776611e-99</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>
@@ -912,13 +874,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3075329594160498</v>
+        <v>0.1285442467678688</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008052894898691507</v>
+        <v>0.009040690178982387</v>
       </c>
       <c r="E13" t="n">
-        <v>381.8911873120559</v>
+        <v>14.21841078756419</v>
       </c>
       <c r="F13" t="n">
         <v>99</v>
@@ -927,15 +889,12 @@
         <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6728416631266818</v>
+        <v>0.6728416631266819</v>
       </c>
       <c r="I13" t="n">
         <v>1.486233767619294</v>
       </c>
-      <c r="J13" t="n">
-        <v>6.148580230983043e-100</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Se rechaza H0</t>
         </is>

--- a/resultados_algoritmos/prueba_F_varianzas.xlsx
+++ b/resultados_algoritmos/prueba_F_varianzas.xlsx
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0003704779512720289</v>
+        <v>0.0003327809654268396</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002475084539854355</v>
+        <v>7.086881511332216e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.496829483221731</v>
+        <v>4.695732035235936</v>
       </c>
       <c r="F2" t="n">
         <v>99</v>
@@ -493,7 +493,7 @@
         <v>99</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I2" t="n">
         <v>1.486233767619294</v>
@@ -514,13 +514,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0003704779512720289</v>
+        <v>0.0003327809654268396</v>
       </c>
       <c r="D3" t="n">
-        <v>7.587553910319367e-05</v>
+        <v>8.134621625516329e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.882706016337683</v>
+        <v>4.090921259115318</v>
       </c>
       <c r="F3" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>99</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I3" t="n">
         <v>1.486233767619294</v>
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0002475084539854355</v>
+        <v>7.086881511332216e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>7.587553910319367e-05</v>
+        <v>8.134621625516329e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.262032229501716</v>
+        <v>0.8711998956537073</v>
       </c>
       <c r="F4" t="n">
         <v>99</v>
@@ -565,14 +565,14 @@
         <v>99</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I4" t="n">
         <v>1.486233767619294</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Se rechaza H0</t>
+          <t>No se rechaza H0</t>
         </is>
       </c>
     </row>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.005290490342966861</v>
+        <v>0.003145031174266608</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004563859959036312</v>
+        <v>0.001402053673282422</v>
       </c>
       <c r="E5" t="n">
-        <v>1.159213996584589</v>
+        <v>2.243160325598384</v>
       </c>
       <c r="F5" t="n">
         <v>99</v>
@@ -601,14 +601,14 @@
         <v>99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I5" t="n">
         <v>1.486233767619294</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>No se rechaza H0</t>
+          <t>Se rechaza H0</t>
         </is>
       </c>
     </row>
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.005290490342966861</v>
+        <v>0.003145031174266608</v>
       </c>
       <c r="D6" t="n">
-        <v>8.184304173084935e-05</v>
+        <v>8.161716053768863e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>64.64190762075134</v>
+        <v>38.53394498837432</v>
       </c>
       <c r="F6" t="n">
         <v>99</v>
@@ -637,7 +637,7 @@
         <v>99</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I6" t="n">
         <v>1.486233767619294</v>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004563859959036312</v>
+        <v>0.001402053673282422</v>
       </c>
       <c r="D7" t="n">
-        <v>8.184304173084935e-05</v>
+        <v>8.161716053768863e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>55.76356721986351</v>
+        <v>17.17841767645165</v>
       </c>
       <c r="F7" t="n">
         <v>99</v>
@@ -673,7 +673,7 @@
         <v>99</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I7" t="n">
         <v>1.486233767619294</v>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04459549578144188</v>
+        <v>0.0171630863041247</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02285683263802575</v>
+        <v>0.1680558172747979</v>
       </c>
       <c r="E8" t="n">
-        <v>1.951079420656501</v>
+        <v>0.102127296647282</v>
       </c>
       <c r="F8" t="n">
         <v>99</v>
@@ -709,7 +709,7 @@
         <v>99</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I8" t="n">
         <v>1.486233767619294</v>
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04459549578144188</v>
+        <v>0.0171630863041247</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004040028083405396</v>
+        <v>0.003707157101716528</v>
       </c>
       <c r="E9" t="n">
-        <v>110.3841232307764</v>
+        <v>4.629716473622784</v>
       </c>
       <c r="F9" t="n">
         <v>99</v>
@@ -745,7 +745,7 @@
         <v>99</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I9" t="n">
         <v>1.486233767619294</v>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02285683263802575</v>
+        <v>0.1680558172747979</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004040028083405396</v>
+        <v>0.003707157101716528</v>
       </c>
       <c r="E10" t="n">
-        <v>56.57592513257831</v>
+        <v>45.33280156834542</v>
       </c>
       <c r="F10" t="n">
         <v>99</v>
@@ -781,7 +781,7 @@
         <v>99</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I10" t="n">
         <v>1.486233767619294</v>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3484503573819249</v>
+        <v>0.08282686570748912</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1285442467678688</v>
+        <v>0.2902438281160716</v>
       </c>
       <c r="E11" t="n">
-        <v>2.710742535301271</v>
+        <v>0.2853699465208465</v>
       </c>
       <c r="F11" t="n">
         <v>99</v>
@@ -817,7 +817,7 @@
         <v>99</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I11" t="n">
         <v>1.486233767619294</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3484503573819249</v>
+        <v>0.08282686570748912</v>
       </c>
       <c r="D12" t="n">
-        <v>0.009040690178982387</v>
+        <v>0.0002751803331328038</v>
       </c>
       <c r="E12" t="n">
-        <v>38.5424509062367</v>
+        <v>300.9912255158014</v>
       </c>
       <c r="F12" t="n">
         <v>99</v>
@@ -853,7 +853,7 @@
         <v>99</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I12" t="n">
         <v>1.486233767619294</v>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1285442467678688</v>
+        <v>0.2902438281160716</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009040690178982387</v>
+        <v>0.0002751803331328038</v>
       </c>
       <c r="E13" t="n">
-        <v>14.21841078756419</v>
+        <v>1054.740448969506</v>
       </c>
       <c r="F13" t="n">
         <v>99</v>
@@ -889,7 +889,7 @@
         <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6728416631266819</v>
+        <v>0.6728416631266818</v>
       </c>
       <c r="I13" t="n">
         <v>1.486233767619294</v>
